--- a/docs/samples/master_data.xlsx
+++ b/docs/samples/master_data.xlsx
@@ -9,12 +9,14 @@
   <sheets>
     <sheet name="归一产品" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="成员条目" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="字段来源" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="库存" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="字段来源" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'归一产品'!$A$1:$M$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'成员条目'!$A$1:$M$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'字段来源'!$A$1:$K$635</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'归一产品'!$A$1:$O$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'成员条目'!$A$1:$O$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'库存'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'字段来源'!$A$1:$K$635</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -446,6 +448,8 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,6 +518,16 @@
           <t>未处理异常数</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>库存合计</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>图片数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -573,6 +587,10 @@
       <c r="M2" t="n">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -632,6 +650,10 @@
       <c r="M3" t="n">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -695,6 +717,10 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -758,6 +784,10 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,6 +847,10 @@
       <c r="M6" t="n">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -876,6 +910,10 @@
       <c r="M7" t="n">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -935,6 +973,10 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -994,6 +1036,10 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1053,6 +1099,10 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1112,6 +1162,10 @@
       <c r="M11" t="n">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1171,6 +1225,10 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1234,6 +1292,10 @@
       <c r="M13" t="n">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1289,6 +1351,10 @@
       <c r="M14" t="n">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1344,6 +1410,10 @@
       <c r="M15" t="n">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1403,6 +1473,10 @@
       <c r="M16" t="n">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1458,6 +1532,10 @@
       <c r="M17" t="n">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1513,6 +1591,10 @@
       <c r="M18" t="n">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1568,6 +1650,10 @@
       <c r="M19" t="n">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1623,6 +1709,10 @@
       <c r="M20" t="n">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1682,6 +1772,10 @@
       <c r="M21" t="n">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1741,6 +1835,10 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1800,6 +1898,10 @@
       <c r="M23" t="n">
         <v>0</v>
       </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1863,6 +1965,10 @@
       <c r="M24" t="n">
         <v>0</v>
       </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1917,6 +2023,10 @@
       </c>
       <c r="M25" t="n">
         <v>3</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1961,6 +2071,10 @@
       <c r="M26" t="n">
         <v>4</v>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2020,6 +2134,10 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2083,6 +2201,10 @@
       <c r="M28" t="n">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2142,6 +2264,10 @@
       <c r="M29" t="n">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2197,6 +2323,10 @@
       <c r="M30" t="n">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2256,6 +2386,10 @@
       <c r="M31" t="n">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2311,6 +2445,10 @@
       <c r="M32" t="n">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2366,6 +2504,10 @@
       <c r="M33" t="n">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2425,6 +2567,10 @@
       <c r="M34" t="n">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2484,6 +2630,10 @@
       <c r="M35" t="n">
         <v>0</v>
       </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2543,6 +2693,10 @@
       <c r="M36" t="n">
         <v>0</v>
       </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2604,6 +2758,10 @@
         </is>
       </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2657,6 +2815,10 @@
       <c r="M38" t="n">
         <v>4</v>
       </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2712,6 +2874,10 @@
       <c r="M39" t="n">
         <v>2</v>
       </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2767,6 +2933,10 @@
       <c r="M40" t="n">
         <v>2</v>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2826,6 +2996,10 @@
       <c r="M41" t="n">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2889,6 +3063,10 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2948,6 +3126,10 @@
       <c r="M43" t="n">
         <v>0</v>
       </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3006,6 +3188,10 @@
       </c>
       <c r="M44" t="n">
         <v>1</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3058,6 +3244,10 @@
       <c r="M45" t="n">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3121,6 +3311,10 @@
       <c r="M46" t="n">
         <v>0</v>
       </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3182,6 +3376,10 @@
         </is>
       </c>
       <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3231,9 +3429,13 @@
       <c r="M48" t="n">
         <v>3</v>
       </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M48"/>
+  <autoFilter ref="A1:O48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3244,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3260,6 +3462,8 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="39" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3328,6 +3532,16 @@
           <t>来源定位</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>图片数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3387,6 +3601,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R2</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3446,6 +3664,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R2</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3505,6 +3727,10 @@
           <t>供应商C目录.pdf!p1!t1!r2</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3564,6 +3790,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R3</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3623,6 +3853,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R3</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3682,6 +3916,10 @@
           <t>供应商C目录.pdf!p1!t1!r3</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3745,6 +3983,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R4</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3808,6 +4050,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R4</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3871,6 +4117,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R5</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3934,6 +4184,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R5</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3993,6 +4247,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R6</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4052,6 +4310,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R6</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4111,6 +4373,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R7</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4170,6 +4436,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R7</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4229,6 +4499,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R8</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4288,6 +4562,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R8</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4347,6 +4625,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R9</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4406,6 +4688,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R9</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4465,6 +4751,10 @@
           <t>供应商C目录.pdf!p1!t1!r5</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4524,6 +4814,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R10</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4583,6 +4877,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R10</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4642,6 +4940,10 @@
           <t>供应商C目录.pdf!p2!t1!r1</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4701,6 +5003,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R11</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4760,6 +5066,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R11</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4815,6 +5125,10 @@
           <t>供应商C目录.pdf!p1!t1!r6</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4874,6 +5188,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R12</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4933,6 +5251,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R12</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4992,6 +5314,10 @@
           <t>供应商C目录.pdf!p1!t1!r7</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5055,6 +5381,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R13</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5110,6 +5440,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R14</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5165,6 +5499,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R15</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5224,6 +5562,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R16</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5279,6 +5621,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R17</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5334,6 +5680,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R18</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5389,6 +5739,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R19</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5444,6 +5798,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R20</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5503,6 +5861,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R21</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5562,6 +5924,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R22</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5621,6 +5987,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R23</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5684,6 +6054,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R24</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5738,6 +6112,10 @@
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R25</t>
         </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5786,6 +6164,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R26</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5845,6 +6227,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R27</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5908,6 +6294,10 @@
           <t>候选人材料_供应商A报价表.xlsx!报价明细!R28</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5967,6 +6357,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R14</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6022,6 +6416,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R15</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6081,6 +6479,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R16</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6136,6 +6538,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R17</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6191,6 +6597,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R18</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6250,6 +6660,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R19</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6309,6 +6723,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R20</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6368,6 +6786,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R21</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6431,6 +6853,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R22</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6486,6 +6912,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R23</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6541,6 +6971,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R24</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6596,6 +7030,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R25</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6655,6 +7093,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R26</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6718,6 +7160,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R27</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6777,6 +7223,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R28</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6835,6 +7285,10 @@
         <is>
           <t>供应商A报价表_v2.xlsx!报价明细!R29</t>
         </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -6891,6 +7345,10 @@
           <t>供应商A报价表_v2.xlsx!报价明细!R30</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6954,6 +7412,10 @@
           <t>候选人材料_供应商B报价表.xlsx!Catalog Export!R13</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7016,6 +7478,10 @@
         <is>
           <t>供应商C目录.pdf!p1!t1!r4</t>
         </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7068,14 +7534,85 @@
           <t>供应商C目录.pdf!p2!t1!r2</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M65"/>
+  <autoFilter ref="A1:O65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>供应商编号</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>截至日期</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>来源定位</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
